--- a/Result/profitability/6270.xlsx
+++ b/Result/profitability/6270.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>0.33625</v>
+        <v>0.33</v>
       </c>
       <c r="N2" t="n">
-        <v>9.421250000000001</v>
+        <v>9.225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0.36125</v>
+        <v>0.34875</v>
       </c>
       <c r="N3" t="n">
-        <v>9.213750000000001</v>
+        <v>8.547499999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.89</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4187500000000001</v>
+        <v>0.435</v>
       </c>
       <c r="N4" t="n">
-        <v>8.58</v>
+        <v>8.605</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0.42</v>
+        <v>0.44375</v>
       </c>
       <c r="N5" t="n">
-        <v>8.8025</v>
+        <v>8.96625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4425</v>
+        <v>0.41625</v>
       </c>
       <c r="N6" t="n">
-        <v>8.983750000000001</v>
+        <v>8.825000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4375</v>
+        <v>0.455</v>
       </c>
       <c r="N7" t="n">
-        <v>8.926250000000001</v>
+        <v>8.717500000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>0.485</v>
+        <v>0.49625</v>
       </c>
       <c r="N8" t="n">
-        <v>8.73625</v>
+        <v>8.55625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6270</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>956</v>
+      </c>
+      <c r="D75" t="n">
+        <v>876</v>
+      </c>
+      <c r="E75" t="n">
+        <v>80</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="G75" t="n">
+        <v>23</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>28</v>
+      </c>
+      <c r="K75" t="n">
+        <v>24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.54125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3750000000000002</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1475409836065573</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.357142857142857</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1868758915834523</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
